--- a/data/trans_camb/P16A10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,82</t>
+          <t>-2,28; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 3,61</t>
+          <t>-2,08; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 6,46</t>
+          <t>-0,41; 6,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,32</t>
+          <t>-2,86; 2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,51</t>
+          <t>-1,21; 4,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 7,22</t>
+          <t>2,15; 7,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 2,15</t>
+          <t>-1,63; 2,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 3,3</t>
+          <t>-0,79; 3,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,13</t>
+          <t>1,84; 5,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 36,48</t>
+          <t>-16,61; 34,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 33,06</t>
+          <t>-15,28; 35,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 58,7</t>
+          <t>-2,85; 54,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 23,19</t>
+          <t>-23,36; 22,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 44,91</t>
+          <t>-10,96; 46,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,88; 74,57</t>
+          <t>17,8; 77,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 20,48</t>
+          <t>-13,28; 19,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 31,29</t>
+          <t>-6,61; 32,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,14; 57,34</t>
+          <t>14,78; 57,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,03</t>
+          <t>-1,05; 0,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,05</t>
+          <t>0,79; 3,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,53</t>
+          <t>-0,06; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,55</t>
+          <t>-1,24; 0,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,77</t>
+          <t>-0,37; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,32</t>
+          <t>-0,54; 1,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,51</t>
+          <t>-0,89; 0,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,06</t>
+          <t>0,64; 2,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,63</t>
+          <t>0,01; 1,58</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 54,39</t>
+          <t>-35,9; 52,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,77; 166,79</t>
+          <t>25,13; 166,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 135,38</t>
+          <t>-1,39; 123,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,89; 45,54</t>
+          <t>-56,73; 46,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 143,98</t>
+          <t>-16,89; 135,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 99,62</t>
+          <t>-23,85; 103,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,7; 32,28</t>
+          <t>-36,53; 28,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,5; 118,44</t>
+          <t>25,13; 125,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 97,31</t>
+          <t>0,85; 93,88</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,65</t>
+          <t>-1,95; 1,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,09</t>
+          <t>-0,94; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,41</t>
+          <t>-0,17; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,03</t>
+          <t>-2,8; 0,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,07</t>
+          <t>-0,85; 3,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,64</t>
+          <t>-1,27; 1,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,53</t>
+          <t>-1,83; 0,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,39</t>
+          <t>-0,2; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,07</t>
+          <t>-0,17; 2,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-72,72; 138,62</t>
+          <t>-70,68; 146,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 280,11</t>
+          <t>-36,58; 266,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 298,69</t>
+          <t>-10,71; 308,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,44</t>
+          <t>-100,0; 91,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 354,55</t>
+          <t>-36,58; 329,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,09; 249,61</t>
+          <t>-48,89; 227,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-74,25; 43,6</t>
+          <t>-73,52; 64,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,3; 195,03</t>
+          <t>-9,8; 230,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 171,3</t>
+          <t>-7,34; 175,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,94</t>
+          <t>-1,19; 1,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,76</t>
+          <t>-0,63; 1,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,13</t>
+          <t>-1,51; 1,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,5</t>
+          <t>-1,58; 0,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,15</t>
+          <t>-0,95; 1,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,59</t>
+          <t>-1,45; 0,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,43</t>
+          <t>-1,04; 0,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,07</t>
+          <t>-0,48; 1,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 0,62</t>
+          <t>-1,16; 0,54</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 19,71</t>
+          <t>-19,53; 22,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 37,94</t>
+          <t>-10,57; 33,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 22,5</t>
+          <t>-25,79; 21,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 10,56</t>
+          <t>-27,13; 12,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 23,67</t>
+          <t>-16,19; 26,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,12; 12,75</t>
+          <t>-24,86; 13,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 8,74</t>
+          <t>-18,31; 8,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 21,93</t>
+          <t>-8,41; 20,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,24; 12,3</t>
+          <t>-20,02; 11,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A10-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>2,34</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>4,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>3,82</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,65</t>
+          <t>-2,35; 3,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 3,85</t>
+          <t>-2,44; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 6,04</t>
+          <t>-1,12; 5,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 2,25</t>
+          <t>-2,79; 2,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,63</t>
+          <t>-1,3; 4,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 7,45</t>
+          <t>2,41; 7,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,09</t>
+          <t>-1,76; 2,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,47</t>
+          <t>-0,89; 3,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,98</t>
+          <t>1,6; 5,9</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 34,94</t>
+          <t>-17,38; 32,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,28; 35,4</t>
+          <t>-17,54; 33,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 54,89</t>
+          <t>-7,89; 51,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,36; 22,91</t>
+          <t>-23,06; 23,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 46,22</t>
+          <t>-10,67; 45,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 77,78</t>
+          <t>18,36; 77,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 19,35</t>
+          <t>-13,96; 19,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 32,25</t>
+          <t>-7,16; 31,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,78; 57,44</t>
+          <t>12,89; 55,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>1,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,94</t>
+          <t>-1,02; 0,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,14</t>
+          <t>0,77; 3,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,35</t>
+          <t>0,62; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,53</t>
+          <t>-1,2; 0,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,74</t>
+          <t>-0,2; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,31</t>
+          <t>-0,17; 1,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,49</t>
+          <t>-0,82; 0,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,17</t>
+          <t>0,53; 2,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,58</t>
+          <t>0,66; 1,94</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,9; 52,34</t>
+          <t>-35,62; 53,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,13; 166,51</t>
+          <t>24,98; 172,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 123,51</t>
+          <t>20,11; 150,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 46,26</t>
+          <t>-57,65; 41,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 135,67</t>
+          <t>-9,78; 140,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,85; 103,2</t>
+          <t>-10,17; 140,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 28,36</t>
+          <t>-33,65; 30,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,13; 125,99</t>
+          <t>20,55; 120,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 93,88</t>
+          <t>27,21; 119,29</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,69</t>
+          <t>-1,92; 1,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,21</t>
+          <t>-0,84; 3,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,49</t>
+          <t>0,1; 3,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,03</t>
+          <t>-2,96; -0,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 3,1</t>
+          <t>-0,79; 3,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,68</t>
+          <t>-1,55; 1,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,55</t>
+          <t>-1,97; 0,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 2,69</t>
+          <t>-0,29; 2,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,15</t>
+          <t>-0,04; 2,35</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>104,41%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>64,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 146,45</t>
+          <t>-69,57; 151,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 266,44</t>
+          <t>-37,29; 249,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 308,04</t>
+          <t>-2,23; 327,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 91,05</t>
+          <t>-100,0; 81,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 329,41</t>
+          <t>-40,78; 371,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 227,14</t>
+          <t>-51,92; 202,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,52; 64,95</t>
+          <t>-75,92; 37,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 230,19</t>
+          <t>-16,48; 191,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 175,48</t>
+          <t>-4,83; 208,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,04</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,09</t>
+          <t>-1,36; 0,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,65</t>
+          <t>-0,42; 1,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,1</t>
+          <t>-0,74; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 0,6</t>
+          <t>-1,58; 0,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,25</t>
+          <t>-1,08; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,65</t>
+          <t>-0,88; 1,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,45</t>
+          <t>-1,02; 0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,04</t>
+          <t>-0,41; 1,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,54</t>
+          <t>-0,48; 0,97</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,13%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-7,09%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,68%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 22,59</t>
+          <t>-22,01; 18,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,57; 33,75</t>
+          <t>-7,26; 37,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 21,04</t>
+          <t>-12,33; 27,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 12,62</t>
+          <t>-27,22; 11,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 26,3</t>
+          <t>-18,58; 23,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 13,49</t>
+          <t>-14,89; 22,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 8,96</t>
+          <t>-18,18; 11,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,41; 20,54</t>
+          <t>-7,26; 23,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 11,02</t>
+          <t>-8,04; 19,96</t>
         </is>
       </c>
     </row>
